--- a/PUBG_Sensitivity_Calculator_v2.2.xlsx
+++ b/PUBG_Sensitivity_Calculator_v2.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="585" windowWidth="37455" windowHeight="17100" activeTab="5"/>
+    <workbookView xWindow="480" yWindow="585" windowWidth="37455" windowHeight="17100"/>
   </bookViews>
   <sheets>
     <sheet name="Korean" sheetId="1" r:id="rId1"/>
@@ -3599,7 +3599,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="67">
-        <f>O7*1.33</f>
+        <f>O7*1.166</f>
         <v>0</v>
       </c>
       <c r="Q15" s="68" t="s">
@@ -3631,7 +3631,7 @@
         <v>-3</v>
       </c>
       <c r="P16" s="69">
-        <f>O7/1.33</f>
+        <f>O7/1.166</f>
         <v>0</v>
       </c>
       <c r="Q16" s="70" t="s">
@@ -8011,6 +8011,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
